--- a/shucle_report/봉양읍/20260101_20260325/report_봉양읍_20260101_20260325.xlsx
+++ b/shucle_report/봉양읍/20260101_20260325/report_봉양읍_20260101_20260325.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +61,12 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
+      <color rgb="001565C0"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -96,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,7 +122,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -505,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.01.01 ~ 03.25 | 비교기간: 2025.10.01 ~ 12.30 | 생성: 2026-03-26 13:09 | 차트: 142개</t>
+          <t>분석기간: 2026.01.01 ~ 03.25 | 비교기간: 2025.10.01 ~ 12.30 | 생성: 2026-03-26 14:48 | 차트: 142개</t>
         </is>
       </c>
     </row>
@@ -943,27 +952,27 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>204km</t>
+          <t>193km</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>223km</t>
+          <t>220km</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>+18.6km</t>
+          <t>+27.2km</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>+9.1%</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>유지</t>
+          <t>+14.1%</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>증가</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1063,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>4.4명</t>
+          <t>4.1명</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>2.1명</t>
+          <t>1.8명</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -1069,7 +1078,7 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-56.0%</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
@@ -1095,7 +1104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1115,7 +1124,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>▲ 평균 대기시간 (+21.2%)</t>
         </is>
@@ -1171,17 +1180,17 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>+5.0</t>
+          <t>+3.6</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1191,7 +1200,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>평일 19.8분 (34% 증가)</t>
+          <t>평일 14.2분 (34% 증가)</t>
         </is>
       </c>
     </row>
@@ -1208,17 +1217,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1228,7 +1237,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>주말 12.2분 (12% 감소)</t>
+          <t>주말 3.5분 (12% 감소)</t>
         </is>
       </c>
     </row>
@@ -1381,9 +1390,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>▲ 평균 경로이탈비중 (+22.7%)</t>
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>▲ 대당 운행거리(일평균) (+14.1%)</t>
         </is>
       </c>
     </row>
@@ -1427,201 +1436,357 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>평균 경로이탈비중</t>
+          <t>대당 운행거리(일평균)</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>평균 우회비율</t>
+          <t>일간 평균 대당 운행거리</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>193</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>220</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>+0.1</t>
+          <t>+27.2</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>+14.1%</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>1.3→1.3배 증가</t>
+          <t>동반 증가 (14%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>평균 경로이탈비중</t>
+          <t>대당 운행거리(일평균)</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>평균 이동시간</t>
+          <t>실시간 호출 건수(일평균)</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>+0.6</t>
+          <t>+2.9</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>+6.8%</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>10.1→10.7분 증가</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>▼ 신규 지역 회원(일평균) (-51.3%)</t>
+          <t>소폭 증가, 영향 제한적</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>대당 운행거리(일평균)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>운행차량 대수</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>+0.0</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>2대 유지, 증차 여지 없음</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>▲ 평균 경로이탈비중 (+22.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>세부지표</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>비교기간</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>분석기간</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>변동값</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>변동률</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>포인트</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>신규 지역 회원(일평균)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>누적 지역 회원(일평균)</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>1,095</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>+237.5</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>+27.7%</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>누적 1095명 (28% 증가)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>평균 경로이탈비중</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>평균 우회비율</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>+0.1</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>+5.6%</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>1.3→1.3배 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>평균 경로이탈비중</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>평균 이동시간</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>+0.6</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>+5.6%</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>10.1→10.7분 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>▼ 신규 지역 회원(일평균) (-56.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>세부지표</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>비교기간</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>분석기간</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>변동값</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>변동률</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t>신규 지역 회원(일평균)</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>누적 지역 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>+124.6</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>+15.6%</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>누적 925명 (16% 증가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>신규 지역 회원(일평균)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>가호출 순 회원(일평균)</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>38.5</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1647,28 +1812,28 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>• 이동완료율 89.5% → 89.9% (+0.4%p): 호출 46건 중 42건 완료 (호출취소 306건, 배차실패 16건)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>• 대기시간 급등: 14.6분 → 17.7분 (+21%) — 특히 02/02 상위10% 대기시간 69.3분으로 극단치 발생</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>• 성장 지표 긍정적: 신규회원 4→2명(-51%), 누적 1166명</t>
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>• 성장 지표 긍정적: 신규회원 4→2명(-56%), 누적 1166명</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>• 수요 현황: 일평균 호출 46.2건(+6.8%), 이동완료 41.5건, 탑승객 47.5명</t>
         </is>
@@ -1688,7 +1853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1708,7 +1873,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>▲ 실시간 호출 건수(일평균) (+6.8%)</t>
         </is>
@@ -2085,7 +2250,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>▲ 이동완료 호출 건수(일평균) (+7.3%)</t>
         </is>
@@ -2240,7 +2405,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>▲ 총 탑승객 수(일평균) (+5.4%)</t>
         </is>
@@ -2432,7 +2597,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>▲ 대당 탑승객 수(일평균) (+3.7%)</t>
         </is>
@@ -2488,17 +2653,17 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>+4.3</t>
+          <t>+3.1</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -2508,7 +2673,7 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>평일 27.8명 (18% 증가)</t>
+          <t>평일 19.9명 (18% 증가)</t>
         </is>
       </c>
     </row>
@@ -2525,17 +2690,17 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -2545,7 +2710,7 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>주말 14.3명 (35% 감소)</t>
+          <t>주말 4.1명 (35% 감소)</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2826,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>▲ 평균 우회비율 (+5.6%)</t>
         </is>
@@ -2816,7 +2981,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>▲ 평균 이동시간 (+5.6%)</t>
         </is>
@@ -2971,7 +3136,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>─ 운행차량 대수 (+0.0%)</t>
         </is>
@@ -3126,7 +3291,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>▼ 대당 운행시간(일평균) (-3.9%)</t>
         </is>
@@ -3280,163 +3445,8 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>▲ 대당 운행거리(일평균) (+9.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>세부지표</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>비교기간</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>분석기간</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>변동값</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>변동률</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>포인트</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>대당 운행거리(일평균)</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>일간 평균 대당 운행거리</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>+18.6</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>+9.1%</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>동반 증가 (9%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>대당 운행거리(일평균)</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>실시간 호출 건수(일평균)</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>46.2</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>+2.9</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>+6.8%</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>동반 증가 (7%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>대당 운행거리(일평균)</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>운행차량 대수</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>+0.0</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>2대 유지, 증차 여지 없음</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
@@ -3445,7 +3455,6 @@
     <mergeCell ref="A54:G54"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A60:G60"/>
     <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
